--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/XRF/Panel 02/front/xrf_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/XRF/Panel 02/front/xrf_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.45184</v>
+        <v>17.74592</v>
       </c>
       <c r="D2" t="n">
-        <v>16.9275</v>
+        <v>17.13208</v>
       </c>
       <c r="E2" t="n">
-        <v>17.09441</v>
+        <v>17.73664</v>
       </c>
       <c r="F2" t="n">
-        <v>44.62609</v>
+        <v>44.07818</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05283</v>
+        <v>0.0535</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8979</v>
+        <v>1.87148</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.60704</v>
+        <v>17.86403</v>
       </c>
       <c r="D3" t="n">
-        <v>17.35172</v>
+        <v>16.92127</v>
       </c>
       <c r="E3" t="n">
-        <v>17.25148</v>
+        <v>17.76006</v>
       </c>
       <c r="F3" t="n">
-        <v>43.10657</v>
+        <v>44.83471</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05251</v>
+        <v>0.05248</v>
       </c>
       <c r="H3" t="n">
-        <v>1.91818</v>
+        <v>1.89062</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.40044</v>
+        <v>17.65965</v>
       </c>
       <c r="D4" t="n">
-        <v>17.52749</v>
+        <v>17.27893</v>
       </c>
       <c r="E4" t="n">
-        <v>17.30728</v>
+        <v>17.60577</v>
       </c>
       <c r="F4" t="n">
-        <v>45.36266</v>
+        <v>44.64663</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05349</v>
+        <v>0.0531</v>
       </c>
       <c r="H4" t="n">
-        <v>1.89433</v>
+        <v>1.90405</v>
       </c>
     </row>
   </sheetData>
